--- a/datasets_ready/smolensk_dataset_shared.xlsx
+++ b/datasets_ready/smolensk_dataset_shared.xlsx
@@ -1,41 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11008"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Kirchik28/Downloads/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7887FA3F-71B6-3B49-9CB3-55E7871A51BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="720" yWindow="1000" windowWidth="24540" windowHeight="13860" xr2:uid="{2572F48F-9375-9C4A-80FE-1D2925AAD219}"/>
+    <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet r:id="rId1" name="Лист1" sheetId="1"/>
   </sheets>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="107">
   <si>
     <t>Современная городская среда</t>
   </si>
@@ -361,25 +361,32 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="171" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="6">
     <font>
+      <b val="0"/>
+      <i val="0"/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="0"/>
+      <i val="0"/>
+      <sz val="11"/>
+      <color auto="1"/>
+      <name val="Carlito"/>
     </font>
     <font>
       <b/>
       <i/>
       <sz val="11"/>
+      <color auto="1"/>
       <name val="Carlito"/>
-      <charset val="204"/>
     </font>
     <font>
       <b/>
@@ -387,20 +394,17 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="Carlito"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Carlito"/>
     </font>
     <font>
       <b/>
+      <i val="0"/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Carlito"/>
     </font>
     <font>
       <b/>
+      <i val="0"/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Carlito"/>
@@ -415,44 +419,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="7" tint="0.6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="9" tint="0.6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="5" tint="0.6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.749992370372631"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="3" tint="0.75"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFE496"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF7030A0"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -474,81 +471,94 @@
       <right/>
       <top/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0">
+      <alignment vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="bottom" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal" xfId="1" xr:uid="{5BE5E2F1-7DC5-C744-9A2A-B9E00214B6F5}"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<FeaturePropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <bag type="Checkbox"/>
+  <bag type="XFControls">
+    <bagId k="CellControl">0</bagId>
+  </bag>
+  <bag type="XFComplement">
+    <bagId k="XFControls">1</bagId>
+  </bag>
+  <bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <a k="MappedFeaturePropertyBags">
+      <bagId>2</bagId>
+    </a>
+  </bag>
+  <bag type="DXFComplements" extRef="DXFComplementsMapperExtRef">
+    <a k="MappedFeaturePropertyBags">
+      <bagId>2</bagId>
+    </a>
+  </bag>
+</FeaturePropertyBags>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -594,7 +604,7 @@
     </a:clrScheme>
     <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -646,7 +656,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -698,7 +708,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -707,151 +717,175 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C005711-1EB7-2E43-AFC5-221F76F5FAF0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{6C18441E-84CC-44C9-AD4F-45BE239E326D}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:AK82"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr defaultRowHeight="15.997499999999997" defaultColWidth="9.00390625" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:37" ht="48">
+    <row r="1" ht="48" customHeight="1">
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
@@ -899,7 +933,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:37" ht="96">
+    <row r="2" ht="96" customHeight="1">
       <c r="A2" s="8" t="s">
         <v>7</v>
       </c>
@@ -1009,7 +1043,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:37" ht="17">
+    <row r="3" ht="17.25" customHeight="1">
       <c r="A3" s="15" t="s">
         <v>27</v>
       </c>
@@ -1032,13 +1066,13 @@
         <v>17</v>
       </c>
       <c r="H3" s="15">
-        <v>35.299999999999997</v>
+        <v>35.3</v>
       </c>
       <c r="I3" s="15">
         <v>70.8</v>
       </c>
       <c r="J3" s="15">
-        <v>19.059999999999999</v>
+        <v>19.06</v>
       </c>
       <c r="K3" s="15">
         <v>43.6</v>
@@ -1062,7 +1096,7 @@
         <v>11</v>
       </c>
       <c r="R3" s="15">
-        <v>66.099999999999994</v>
+        <v>66.1</v>
       </c>
       <c r="S3" s="15">
         <v>4</v>
@@ -1071,7 +1105,7 @@
         <v>3612</v>
       </c>
       <c r="U3" s="15">
-        <v>67.900000000000006</v>
+        <v>67.9</v>
       </c>
       <c r="V3" s="15">
         <v>8</v>
@@ -1083,7 +1117,7 @@
         <v>72.8</v>
       </c>
       <c r="Y3" s="15">
-        <v>10.199999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="Z3" s="15">
         <v>54.3</v>
@@ -1119,7 +1153,7 @@
         <v>37.9</v>
       </c>
     </row>
-    <row r="4" spans="1:37" ht="17">
+    <row r="4" ht="17.25" customHeight="1">
       <c r="A4" s="15" t="s">
         <v>28</v>
       </c>
@@ -1190,7 +1224,7 @@
         <v>54.4</v>
       </c>
       <c r="X4" s="15">
-        <v>77.099999999999994</v>
+        <v>77.1</v>
       </c>
       <c r="Y4" s="15">
         <v>22.369999999999997</v>
@@ -1217,7 +1251,7 @@
         <v>23</v>
       </c>
       <c r="AG4" s="15">
-        <v>75.099999999999994</v>
+        <v>75.1</v>
       </c>
       <c r="AH4" s="15">
         <v>3.35</v>
@@ -1229,7 +1263,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:37" ht="17">
+    <row r="5" ht="17.25" customHeight="1">
       <c r="A5" s="15" t="s">
         <v>29</v>
       </c>
@@ -1246,13 +1280,13 @@
         <v>3</v>
       </c>
       <c r="F5" s="15">
-        <v>76.599999999999994</v>
+        <v>76.6</v>
       </c>
       <c r="G5" s="15">
         <v>31</v>
       </c>
       <c r="H5" s="15">
-        <v>36.299999999999997</v>
+        <v>36.3</v>
       </c>
       <c r="I5" s="15">
         <v>78.3</v>
@@ -1273,7 +1307,7 @@
         <v>19.7</v>
       </c>
       <c r="O5" s="15">
-        <v>37.299999999999997</v>
+        <v>37.3</v>
       </c>
       <c r="P5" s="15">
         <v>41.5</v>
@@ -1300,7 +1334,7 @@
         <v>55</v>
       </c>
       <c r="X5" s="15">
-        <v>81.599999999999994</v>
+        <v>81.6</v>
       </c>
       <c r="Y5" s="15">
         <v>27.81</v>
@@ -1339,7 +1373,7 @@
         <v>36.1</v>
       </c>
     </row>
-    <row r="6" spans="1:37" ht="17">
+    <row r="6" ht="17.25" customHeight="1">
       <c r="A6" s="15" t="s">
         <v>30</v>
       </c>
@@ -1362,7 +1396,7 @@
         <v>33</v>
       </c>
       <c r="H6" s="15">
-        <v>35.200000000000003</v>
+        <v>35.2</v>
       </c>
       <c r="I6" s="15">
         <v>85.3</v>
@@ -1386,7 +1420,7 @@
         <v>40</v>
       </c>
       <c r="P6" s="15">
-        <v>40.700000000000003</v>
+        <v>40.7</v>
       </c>
       <c r="Q6" s="15">
         <v>20</v>
@@ -1449,7 +1483,7 @@
         <v>36.4</v>
       </c>
     </row>
-    <row r="7" spans="1:37" ht="17">
+    <row r="7" ht="17.25" customHeight="1">
       <c r="A7" s="15" t="s">
         <v>31</v>
       </c>
@@ -1496,7 +1530,7 @@
         <v>40.5</v>
       </c>
       <c r="P7" s="15">
-        <v>40.700000000000003</v>
+        <v>40.7</v>
       </c>
       <c r="Q7" s="15">
         <v>11</v>
@@ -1547,7 +1581,7 @@
         <v>16</v>
       </c>
       <c r="AG7" s="15">
-        <v>72.400000000000006</v>
+        <v>72.4</v>
       </c>
       <c r="AH7" s="15">
         <v>1.51</v>
@@ -1559,7 +1593,7 @@
         <v>39.5</v>
       </c>
     </row>
-    <row r="8" spans="1:37" ht="17">
+    <row r="8" ht="17.25" customHeight="1">
       <c r="A8" s="15" t="s">
         <v>32</v>
       </c>
@@ -1576,13 +1610,13 @@
         <v>6</v>
       </c>
       <c r="F8" s="15">
-        <v>76.099999999999994</v>
+        <v>76.1</v>
       </c>
       <c r="G8" s="15">
         <v>25</v>
       </c>
       <c r="H8" s="15">
-        <v>34.200000000000003</v>
+        <v>34.2</v>
       </c>
       <c r="I8" s="15">
         <v>78</v>
@@ -1666,10 +1700,10 @@
         <v>61.9</v>
       </c>
       <c r="AJ8" s="15">
-        <v>38.200000000000003</v>
+        <v>38.2</v>
       </c>
     </row>
-    <row r="9" spans="1:37" ht="17">
+    <row r="9" ht="17.25" customHeight="1">
       <c r="A9" s="15" t="s">
         <v>33</v>
       </c>
@@ -1710,10 +1744,10 @@
         <v>50.3</v>
       </c>
       <c r="N9" s="15">
-        <v>19.899999999999999</v>
+        <v>19.9</v>
       </c>
       <c r="O9" s="15">
-        <v>35.200000000000003</v>
+        <v>35.2</v>
       </c>
       <c r="P9" s="15">
         <v>40.5</v>
@@ -1776,10 +1810,10 @@
         <v>61.4</v>
       </c>
       <c r="AJ9" s="15">
-        <v>34.700000000000003</v>
+        <v>34.7</v>
       </c>
     </row>
-    <row r="10" spans="1:37" ht="17">
+    <row r="10" ht="17.25" customHeight="1">
       <c r="A10" s="15" t="s">
         <v>34</v>
       </c>
@@ -1823,10 +1857,10 @@
         <v>21.7</v>
       </c>
       <c r="O10" s="15">
-        <v>38.299999999999997</v>
+        <v>38.3</v>
       </c>
       <c r="P10" s="15">
-        <v>40.299999999999997</v>
+        <v>40.3</v>
       </c>
       <c r="Q10" s="15">
         <v>22</v>
@@ -1859,7 +1893,7 @@
         <v>55.7</v>
       </c>
       <c r="AA10" s="15">
-        <v>40.200000000000003</v>
+        <v>40.2</v>
       </c>
       <c r="AB10" s="15">
         <v>59</v>
@@ -1886,10 +1920,10 @@
         <v>61.8</v>
       </c>
       <c r="AJ10" s="15">
-        <v>33.200000000000003</v>
+        <v>33.2</v>
       </c>
     </row>
-    <row r="11" spans="1:37" ht="17">
+    <row r="11" ht="17.25" customHeight="1">
       <c r="A11" s="15" t="s">
         <v>35</v>
       </c>
@@ -1912,13 +1946,13 @@
         <v>18</v>
       </c>
       <c r="H11" s="15">
-        <v>35.799999999999997</v>
+        <v>35.8</v>
       </c>
       <c r="I11" s="15">
         <v>69.3</v>
       </c>
       <c r="J11" s="15">
-        <v>18.760000000000002</v>
+        <v>18.76</v>
       </c>
       <c r="K11" s="15">
         <v>42.4</v>
@@ -1930,19 +1964,19 @@
         <v>52.4</v>
       </c>
       <c r="N11" s="15">
-        <v>20.399999999999999</v>
+        <v>20.4</v>
       </c>
       <c r="O11" s="15">
         <v>42.7</v>
       </c>
       <c r="P11" s="15">
-        <v>39.799999999999997</v>
+        <v>39.8</v>
       </c>
       <c r="Q11" s="15">
         <v>11</v>
       </c>
       <c r="R11" s="15">
-        <v>72.900000000000006</v>
+        <v>72.9</v>
       </c>
       <c r="S11" s="15">
         <v>5</v>
@@ -1951,7 +1985,7 @@
         <v>3320</v>
       </c>
       <c r="U11" s="15">
-        <v>68.900000000000006</v>
+        <v>68.9</v>
       </c>
       <c r="V11" s="15">
         <v>8</v>
@@ -1969,7 +2003,7 @@
         <v>55.2</v>
       </c>
       <c r="AA11" s="15">
-        <v>37.299999999999997</v>
+        <v>37.3</v>
       </c>
       <c r="AB11" s="15">
         <v>58.9</v>
@@ -1999,7 +2033,7 @@
         <v>35.1</v>
       </c>
     </row>
-    <row r="12" spans="1:37" ht="17">
+    <row r="12" ht="17.25" customHeight="1">
       <c r="A12" s="15" t="s">
         <v>36</v>
       </c>
@@ -2016,13 +2050,13 @@
         <v>10</v>
       </c>
       <c r="F12" s="15">
-        <v>75.599999999999994</v>
+        <v>75.6</v>
       </c>
       <c r="G12" s="15">
         <v>25</v>
       </c>
       <c r="H12" s="15">
-        <v>35.700000000000003</v>
+        <v>35.7</v>
       </c>
       <c r="I12" s="15">
         <v>75.7</v>
@@ -2046,7 +2080,7 @@
         <v>32.9</v>
       </c>
       <c r="P12" s="15">
-        <v>36.299999999999997</v>
+        <v>36.3</v>
       </c>
       <c r="Q12" s="15">
         <v>16</v>
@@ -2109,7 +2143,7 @@
         <v>34.9</v>
       </c>
     </row>
-    <row r="13" spans="1:37" ht="17">
+    <row r="13" ht="17.25" customHeight="1">
       <c r="A13" s="15" t="s">
         <v>37</v>
       </c>
@@ -2135,7 +2169,7 @@
         <v>35.9</v>
       </c>
       <c r="I13" s="15">
-        <v>78.400000000000006</v>
+        <v>78.4</v>
       </c>
       <c r="J13" s="15">
         <v>49.96</v>
@@ -2156,13 +2190,13 @@
         <v>32.9</v>
       </c>
       <c r="P13" s="15">
-        <v>39.799999999999997</v>
+        <v>39.8</v>
       </c>
       <c r="Q13" s="15">
         <v>19</v>
       </c>
       <c r="R13" s="15">
-        <v>80.099999999999994</v>
+        <v>80.1</v>
       </c>
       <c r="S13" s="15">
         <v>8</v>
@@ -2216,10 +2250,10 @@
         <v>59.1</v>
       </c>
       <c r="AJ13" s="15">
-        <v>32.299999999999997</v>
+        <v>32.3</v>
       </c>
     </row>
-    <row r="14" spans="1:37" ht="17">
+    <row r="14" ht="17.25" customHeight="1">
       <c r="A14" s="15" t="s">
         <v>38</v>
       </c>
@@ -2263,10 +2297,10 @@
         <v>21.6</v>
       </c>
       <c r="O14" s="15">
-        <v>36.200000000000003</v>
+        <v>36.2</v>
       </c>
       <c r="P14" s="15">
-        <v>37.200000000000003</v>
+        <v>37.2</v>
       </c>
       <c r="Q14" s="15">
         <v>22</v>
@@ -2308,7 +2342,7 @@
         <v>25.9</v>
       </c>
       <c r="AD14" s="15">
-        <v>19.399999999999999</v>
+        <v>19.4</v>
       </c>
       <c r="AE14" s="15">
         <v>5.5</v>
@@ -2326,10 +2360,10 @@
         <v>65.8</v>
       </c>
       <c r="AJ14" s="15">
-        <v>34.299999999999997</v>
+        <v>34.3</v>
       </c>
     </row>
-    <row r="15" spans="1:37" ht="17">
+    <row r="15" ht="17.25" customHeight="1">
       <c r="A15" s="15" t="s">
         <v>39</v>
       </c>
@@ -2346,7 +2380,7 @@
         <v>13</v>
       </c>
       <c r="F15" s="15">
-        <v>67.400000000000006</v>
+        <v>67.4</v>
       </c>
       <c r="G15" s="15">
         <v>17</v>
@@ -2364,7 +2398,7 @@
         <v>42</v>
       </c>
       <c r="L15" s="15">
-        <v>80.900000000000006</v>
+        <v>80.9</v>
       </c>
       <c r="M15" s="15">
         <v>53.6</v>
@@ -2376,13 +2410,13 @@
         <v>39</v>
       </c>
       <c r="P15" s="15">
-        <v>38.299999999999997</v>
+        <v>38.3</v>
       </c>
       <c r="Q15" s="15">
         <v>11</v>
       </c>
       <c r="R15" s="15">
-        <v>68.900000000000006</v>
+        <v>68.9</v>
       </c>
       <c r="S15" s="15">
         <v>4</v>
@@ -2409,7 +2443,7 @@
         <v>57.2</v>
       </c>
       <c r="AA15" s="15">
-        <v>36.299999999999997</v>
+        <v>36.3</v>
       </c>
       <c r="AB15" s="15">
         <v>58.1</v>
@@ -2436,10 +2470,10 @@
         <v>62.9</v>
       </c>
       <c r="AJ15" s="15">
-        <v>32.799999999999997</v>
+        <v>32.8</v>
       </c>
     </row>
-    <row r="16" spans="1:37" ht="17">
+    <row r="16" ht="17.25" customHeight="1">
       <c r="A16" s="15" t="s">
         <v>40</v>
       </c>
@@ -2480,13 +2514,13 @@
         <v>53.8</v>
       </c>
       <c r="N16" s="15">
-        <v>19.899999999999999</v>
+        <v>19.9</v>
       </c>
       <c r="O16" s="15">
-        <v>37.200000000000003</v>
+        <v>37.2</v>
       </c>
       <c r="P16" s="15">
-        <v>37.799999999999997</v>
+        <v>37.8</v>
       </c>
       <c r="Q16" s="15">
         <v>16</v>
@@ -2501,7 +2535,7 @@
         <v>3983</v>
       </c>
       <c r="U16" s="15">
-        <v>76.099999999999994</v>
+        <v>76.1</v>
       </c>
       <c r="V16" s="15">
         <v>11</v>
@@ -2510,7 +2544,7 @@
         <v>58</v>
       </c>
       <c r="X16" s="15">
-        <v>75.400000000000006</v>
+        <v>75.4</v>
       </c>
       <c r="Y16" s="15">
         <v>25.04</v>
@@ -2537,7 +2571,7 @@
         <v>22</v>
       </c>
       <c r="AG16" s="15">
-        <v>78.400000000000006</v>
+        <v>78.4</v>
       </c>
       <c r="AH16" s="15">
         <v>3.1</v>
@@ -2549,7 +2583,7 @@
         <v>33.5</v>
       </c>
     </row>
-    <row r="17" spans="1:36" ht="17">
+    <row r="17" ht="17.25" customHeight="1">
       <c r="A17" s="15" t="s">
         <v>41</v>
       </c>
@@ -2611,7 +2645,7 @@
         <v>4526</v>
       </c>
       <c r="U17" s="15">
-        <v>79.099999999999994</v>
+        <v>79.1</v>
       </c>
       <c r="V17" s="15">
         <v>14</v>
@@ -2647,7 +2681,7 @@
         <v>26</v>
       </c>
       <c r="AG17" s="15">
-        <v>80.099999999999994</v>
+        <v>80.1</v>
       </c>
       <c r="AH17" s="15">
         <v>3.78</v>
@@ -2659,7 +2693,7 @@
         <v>31.5</v>
       </c>
     </row>
-    <row r="18" spans="1:36" ht="17">
+    <row r="18" ht="17.25" customHeight="1">
       <c r="A18" s="15" t="s">
         <v>42</v>
       </c>
@@ -2703,7 +2737,7 @@
         <v>20.7</v>
       </c>
       <c r="O18" s="15">
-        <v>35.200000000000003</v>
+        <v>35.2</v>
       </c>
       <c r="P18" s="15">
         <v>37.9</v>
@@ -2769,7 +2803,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:36" ht="17">
+    <row r="19" ht="17.25" customHeight="1">
       <c r="A19" s="15" t="s">
         <v>43</v>
       </c>
@@ -2795,7 +2829,7 @@
         <v>39</v>
       </c>
       <c r="I19" s="15">
-        <v>70.400000000000006</v>
+        <v>70.4</v>
       </c>
       <c r="J19" s="15">
         <v>19.61</v>
@@ -2813,10 +2847,10 @@
         <v>17.8</v>
       </c>
       <c r="O19" s="15">
-        <v>38.799999999999997</v>
+        <v>38.8</v>
       </c>
       <c r="P19" s="15">
-        <v>39.299999999999997</v>
+        <v>39.3</v>
       </c>
       <c r="Q19" s="15">
         <v>13</v>
@@ -2840,7 +2874,7 @@
         <v>53.1</v>
       </c>
       <c r="X19" s="15">
-        <v>73.900000000000006</v>
+        <v>73.9</v>
       </c>
       <c r="Y19" s="15">
         <v>12.27</v>
@@ -2879,7 +2913,7 @@
         <v>30.3</v>
       </c>
     </row>
-    <row r="20" spans="1:36" ht="17">
+    <row r="20" ht="17.25" customHeight="1">
       <c r="A20" s="15" t="s">
         <v>44</v>
       </c>
@@ -2896,13 +2930,13 @@
         <v>18</v>
       </c>
       <c r="F20" s="15">
-        <v>78.400000000000006</v>
+        <v>78.4</v>
       </c>
       <c r="G20" s="15">
         <v>28</v>
       </c>
       <c r="H20" s="15">
-        <v>39.299999999999997</v>
+        <v>39.3</v>
       </c>
       <c r="I20" s="15">
         <v>78.7</v>
@@ -2926,7 +2960,7 @@
         <v>35.1</v>
       </c>
       <c r="P20" s="15">
-        <v>37.700000000000003</v>
+        <v>37.7</v>
       </c>
       <c r="Q20" s="15">
         <v>18</v>
@@ -2941,7 +2975,7 @@
         <v>4129</v>
       </c>
       <c r="U20" s="15">
-        <v>75.400000000000006</v>
+        <v>75.4</v>
       </c>
       <c r="V20" s="15">
         <v>13</v>
@@ -2968,7 +3002,7 @@
         <v>26.8</v>
       </c>
       <c r="AD20" s="15">
-        <v>18.100000000000001</v>
+        <v>18.1</v>
       </c>
       <c r="AE20" s="15">
         <v>5.9</v>
@@ -2977,7 +3011,7 @@
         <v>24</v>
       </c>
       <c r="AG20" s="15">
-        <v>75.400000000000006</v>
+        <v>75.4</v>
       </c>
       <c r="AH20" s="15">
         <v>3.05</v>
@@ -2986,10 +3020,10 @@
         <v>61.7</v>
       </c>
       <c r="AJ20" s="15">
-        <v>32.799999999999997</v>
+        <v>32.8</v>
       </c>
     </row>
-    <row r="21" spans="1:36" ht="17">
+    <row r="21" ht="17.25" customHeight="1">
       <c r="A21" s="15" t="s">
         <v>45</v>
       </c>
@@ -3024,13 +3058,13 @@
         <v>44.3</v>
       </c>
       <c r="L21" s="15">
-        <v>128.80000000000001</v>
+        <v>128.8</v>
       </c>
       <c r="M21" s="15">
         <v>57.2</v>
       </c>
       <c r="N21" s="15">
-        <v>18.899999999999999</v>
+        <v>18.9</v>
       </c>
       <c r="O21" s="15">
         <v>33.1</v>
@@ -3042,7 +3076,7 @@
         <v>23</v>
       </c>
       <c r="R21" s="15">
-        <v>81.599999999999994</v>
+        <v>81.6</v>
       </c>
       <c r="S21" s="15">
         <v>9</v>
@@ -3096,10 +3130,10 @@
         <v>59.9</v>
       </c>
       <c r="AJ21" s="15">
-        <v>32.299999999999997</v>
+        <v>32.3</v>
       </c>
     </row>
-    <row r="22" spans="1:36" ht="17">
+    <row r="22" ht="17.25" customHeight="1">
       <c r="A22" s="15" t="s">
         <v>46</v>
       </c>
@@ -3146,7 +3180,7 @@
         <v>36.9</v>
       </c>
       <c r="P22" s="15">
-        <v>39.299999999999997</v>
+        <v>39.3</v>
       </c>
       <c r="Q22" s="15">
         <v>25</v>
@@ -3206,10 +3240,10 @@
         <v>61.4</v>
       </c>
       <c r="AJ22" s="15">
-        <v>32.299999999999997</v>
+        <v>32.3</v>
       </c>
     </row>
-    <row r="23" spans="1:36" ht="17">
+    <row r="23" ht="17.25" customHeight="1">
       <c r="A23" s="15" t="s">
         <v>47</v>
       </c>
@@ -3226,13 +3260,13 @@
         <v>21</v>
       </c>
       <c r="F23" s="15">
-        <v>70.599999999999994</v>
+        <v>70.6</v>
       </c>
       <c r="G23" s="15">
         <v>20</v>
       </c>
       <c r="H23" s="15">
-        <v>39.299999999999997</v>
+        <v>39.3</v>
       </c>
       <c r="I23" s="15">
         <v>74.7</v>
@@ -3256,7 +3290,7 @@
         <v>41.4</v>
       </c>
       <c r="P23" s="15">
-        <v>37.799999999999997</v>
+        <v>37.8</v>
       </c>
       <c r="Q23" s="15">
         <v>13</v>
@@ -3298,7 +3332,7 @@
         <v>28.9</v>
       </c>
       <c r="AD23" s="15">
-        <v>17.100000000000001</v>
+        <v>17.1</v>
       </c>
       <c r="AE23" s="15">
         <v>6</v>
@@ -3307,7 +3341,7 @@
         <v>17</v>
       </c>
       <c r="AG23" s="15">
-        <v>70.099999999999994</v>
+        <v>70.1</v>
       </c>
       <c r="AH23" s="15">
         <v>1.43</v>
@@ -3319,7 +3353,7 @@
         <v>32.1</v>
       </c>
     </row>
-    <row r="24" spans="1:36" ht="17">
+    <row r="24" ht="17.25" customHeight="1">
       <c r="A24" s="15" t="s">
         <v>48</v>
       </c>
@@ -3336,7 +3370,7 @@
         <v>22</v>
       </c>
       <c r="F24" s="15">
-        <v>78.400000000000006</v>
+        <v>78.4</v>
       </c>
       <c r="G24" s="15">
         <v>28</v>
@@ -3381,7 +3415,7 @@
         <v>4018</v>
       </c>
       <c r="U24" s="15">
-        <v>79.099999999999994</v>
+        <v>79.1</v>
       </c>
       <c r="V24" s="15">
         <v>12</v>
@@ -3417,7 +3451,7 @@
         <v>26</v>
       </c>
       <c r="AG24" s="15">
-        <v>77.400000000000006</v>
+        <v>77.4</v>
       </c>
       <c r="AH24" s="15">
         <v>3.15</v>
@@ -3426,10 +3460,10 @@
         <v>61.5</v>
       </c>
       <c r="AJ24" s="15">
-        <v>32.200000000000003</v>
+        <v>32.2</v>
       </c>
     </row>
-    <row r="25" spans="1:36" ht="17">
+    <row r="25" ht="17.25" customHeight="1">
       <c r="A25" s="15" t="s">
         <v>49</v>
       </c>
@@ -3458,7 +3492,7 @@
         <v>81.2</v>
       </c>
       <c r="J25" s="15">
-        <v>59.429999999999993</v>
+        <v>59.42999999999999</v>
       </c>
       <c r="K25" s="15">
         <v>44.9</v>
@@ -3473,10 +3507,10 @@
         <v>21.2</v>
       </c>
       <c r="O25" s="15">
-        <v>32.200000000000003</v>
+        <v>32.2</v>
       </c>
       <c r="P25" s="15">
-        <v>38.200000000000003</v>
+        <v>38.2</v>
       </c>
       <c r="Q25" s="15">
         <v>26</v>
@@ -3491,7 +3525,7 @@
         <v>4605</v>
       </c>
       <c r="U25" s="15">
-        <v>81.599999999999994</v>
+        <v>81.6</v>
       </c>
       <c r="V25" s="15">
         <v>14</v>
@@ -3500,7 +3534,7 @@
         <v>56.8</v>
       </c>
       <c r="X25" s="15">
-        <v>81.400000000000006</v>
+        <v>81.4</v>
       </c>
       <c r="Y25" s="15">
         <v>34.489999999999995</v>
@@ -3509,7 +3543,7 @@
         <v>58.4</v>
       </c>
       <c r="AA25" s="15">
-        <v>65.400000000000006</v>
+        <v>65.4</v>
       </c>
       <c r="AB25" s="15">
         <v>57</v>
@@ -3527,7 +3561,7 @@
         <v>30</v>
       </c>
       <c r="AG25" s="15">
-        <v>79.099999999999994</v>
+        <v>79.1</v>
       </c>
       <c r="AH25" s="15">
         <v>4.03</v>
@@ -3536,10 +3570,10 @@
         <v>59.9</v>
       </c>
       <c r="AJ25" s="15">
-        <v>32.299999999999997</v>
+        <v>32.3</v>
       </c>
     </row>
-    <row r="26" spans="1:36" ht="17">
+    <row r="26" ht="17.25" customHeight="1">
       <c r="A26" s="15" t="s">
         <v>50</v>
       </c>
@@ -3580,13 +3614,13 @@
         <v>57.9</v>
       </c>
       <c r="N26" s="15">
-        <v>19.100000000000001</v>
+        <v>19.1</v>
       </c>
       <c r="O26" s="15">
-        <v>39.700000000000003</v>
+        <v>39.7</v>
       </c>
       <c r="P26" s="15">
-        <v>38.200000000000003</v>
+        <v>38.2</v>
       </c>
       <c r="Q26" s="15">
         <v>27</v>
@@ -3649,7 +3683,7 @@
         <v>32.5</v>
       </c>
     </row>
-    <row r="27" spans="1:36" ht="17">
+    <row r="27" ht="17.25" customHeight="1">
       <c r="A27" s="15" t="s">
         <v>51</v>
       </c>
@@ -3675,7 +3709,7 @@
         <v>41.2</v>
       </c>
       <c r="I27" s="15">
-        <v>75.400000000000006</v>
+        <v>75.4</v>
       </c>
       <c r="J27" s="15">
         <v>21.5</v>
@@ -3696,7 +3730,7 @@
         <v>39</v>
       </c>
       <c r="P27" s="15">
-        <v>38.700000000000003</v>
+        <v>38.7</v>
       </c>
       <c r="Q27" s="15">
         <v>13</v>
@@ -3720,7 +3754,7 @@
         <v>55.7</v>
       </c>
       <c r="X27" s="15">
-        <v>74.099999999999994</v>
+        <v>74.1</v>
       </c>
       <c r="Y27" s="15">
         <v>12.899999999999999</v>
@@ -3741,13 +3775,13 @@
         <v>17.2</v>
       </c>
       <c r="AE27" s="15">
-        <v>5.0999999999999996</v>
+        <v>5.1</v>
       </c>
       <c r="AF27" s="15">
         <v>17</v>
       </c>
       <c r="AG27" s="15">
-        <v>74.400000000000006</v>
+        <v>74.4</v>
       </c>
       <c r="AH27" s="15">
         <v>1.47</v>
@@ -3759,7 +3793,7 @@
         <v>31.5</v>
       </c>
     </row>
-    <row r="28" spans="1:36" ht="17">
+    <row r="28" ht="17.25" customHeight="1">
       <c r="A28" s="15" t="s">
         <v>52</v>
       </c>
@@ -3803,7 +3837,7 @@
         <v>18.8</v>
       </c>
       <c r="O28" s="15">
-        <v>35.200000000000003</v>
+        <v>35.2</v>
       </c>
       <c r="P28" s="15">
         <v>39</v>
@@ -3812,7 +3846,7 @@
         <v>20</v>
       </c>
       <c r="R28" s="15">
-        <v>76.099999999999994</v>
+        <v>76.1</v>
       </c>
       <c r="S28" s="15">
         <v>7</v>
@@ -3821,7 +3855,7 @@
         <v>4407</v>
       </c>
       <c r="U28" s="15">
-        <v>77.900000000000006</v>
+        <v>77.9</v>
       </c>
       <c r="V28" s="15">
         <v>12</v>
@@ -3857,7 +3891,7 @@
         <v>26</v>
       </c>
       <c r="AG28" s="15">
-        <v>75.900000000000006</v>
+        <v>75.9</v>
       </c>
       <c r="AH28" s="15">
         <v>3.19</v>
@@ -3869,7 +3903,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:36" ht="17">
+    <row r="29" ht="17.25" customHeight="1">
       <c r="A29" s="15" t="s">
         <v>53</v>
       </c>
@@ -3913,7 +3947,7 @@
         <v>17.7</v>
       </c>
       <c r="O29" s="15">
-        <v>32.700000000000003</v>
+        <v>32.7</v>
       </c>
       <c r="P29" s="15">
         <v>36.9</v>
@@ -3949,7 +3983,7 @@
         <v>57.6</v>
       </c>
       <c r="AA29" s="15">
-        <v>64.900000000000006</v>
+        <v>64.9</v>
       </c>
       <c r="AB29" s="15">
         <v>57.6</v>
@@ -3970,7 +4004,7 @@
         <v>82.1</v>
       </c>
       <c r="AH29" s="15">
-        <v>4.0999999999999996</v>
+        <v>4.1</v>
       </c>
       <c r="AI29" s="15">
         <v>58.8</v>
@@ -3979,7 +4013,7 @@
         <v>31.8</v>
       </c>
     </row>
-    <row r="30" spans="1:36" ht="17">
+    <row r="30" ht="17.25" customHeight="1">
       <c r="A30" s="15" t="s">
         <v>54</v>
       </c>
@@ -4089,7 +4123,7 @@
         <v>30.6</v>
       </c>
     </row>
-    <row r="31" spans="1:36" ht="17">
+    <row r="31" ht="17.25" customHeight="1">
       <c r="A31" s="15" t="s">
         <v>55</v>
       </c>
@@ -4130,13 +4164,13 @@
         <v>58.6</v>
       </c>
       <c r="N31" s="15">
-        <v>19.100000000000001</v>
+        <v>19.1</v>
       </c>
       <c r="O31" s="15">
         <v>38.6</v>
       </c>
       <c r="P31" s="15">
-        <v>37.700000000000003</v>
+        <v>37.7</v>
       </c>
       <c r="Q31" s="15">
         <v>14</v>
@@ -4178,10 +4212,10 @@
         <v>28.2</v>
       </c>
       <c r="AD31" s="15">
-        <v>18.600000000000001</v>
+        <v>18.6</v>
       </c>
       <c r="AE31" s="15">
-        <v>5.0999999999999996</v>
+        <v>5.1</v>
       </c>
       <c r="AF31" s="15">
         <v>19</v>
@@ -4199,7 +4233,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:36" ht="17">
+    <row r="32" ht="17.25" customHeight="1">
       <c r="A32" s="15" t="s">
         <v>56</v>
       </c>
@@ -4252,7 +4286,7 @@
         <v>20</v>
       </c>
       <c r="R32" s="15">
-        <v>75.900000000000006</v>
+        <v>75.9</v>
       </c>
       <c r="S32" s="15">
         <v>7</v>
@@ -4270,7 +4304,7 @@
         <v>54.5</v>
       </c>
       <c r="X32" s="15">
-        <v>79.900000000000006</v>
+        <v>79.9</v>
       </c>
       <c r="Y32" s="15">
         <v>27.86</v>
@@ -4288,16 +4322,16 @@
         <v>28.7</v>
       </c>
       <c r="AD32" s="15">
-        <v>16.600000000000001</v>
+        <v>16.6</v>
       </c>
       <c r="AE32" s="15">
-        <v>5.0999999999999996</v>
+        <v>5.1</v>
       </c>
       <c r="AF32" s="15">
         <v>27</v>
       </c>
       <c r="AG32" s="15">
-        <v>77.900000000000006</v>
+        <v>77.9</v>
       </c>
       <c r="AH32" s="15">
         <v>3.61</v>
@@ -4306,10 +4340,10 @@
         <v>60.3</v>
       </c>
       <c r="AJ32" s="15">
-        <v>32.200000000000003</v>
+        <v>32.2</v>
       </c>
     </row>
-    <row r="33" spans="1:36" ht="17">
+    <row r="33" ht="17.25" customHeight="1">
       <c r="A33" s="15" t="s">
         <v>57</v>
       </c>
@@ -4344,7 +4378,7 @@
         <v>43.2</v>
       </c>
       <c r="L33" s="15">
-        <v>157.69999999999999</v>
+        <v>157.7</v>
       </c>
       <c r="M33" s="15">
         <v>61.1</v>
@@ -4371,7 +4405,7 @@
         <v>4686</v>
       </c>
       <c r="U33" s="15">
-        <v>81.900000000000006</v>
+        <v>81.9</v>
       </c>
       <c r="V33" s="15">
         <v>14</v>
@@ -4419,7 +4453,7 @@
         <v>30.7</v>
       </c>
     </row>
-    <row r="34" spans="1:36" ht="17">
+    <row r="34" ht="17.25" customHeight="1">
       <c r="A34" s="15" t="s">
         <v>58</v>
       </c>
@@ -4460,10 +4494,10 @@
         <v>60.1</v>
       </c>
       <c r="N34" s="15">
-        <v>17.600000000000001</v>
+        <v>17.6</v>
       </c>
       <c r="O34" s="15">
-        <v>35.200000000000003</v>
+        <v>35.2</v>
       </c>
       <c r="P34" s="15">
         <v>37.6</v>
@@ -4508,10 +4542,10 @@
         <v>29.3</v>
       </c>
       <c r="AD34" s="15">
-        <v>16.100000000000001</v>
+        <v>16.1</v>
       </c>
       <c r="AE34" s="15">
-        <v>5.0999999999999996</v>
+        <v>5.1</v>
       </c>
       <c r="AF34" s="15">
         <v>35</v>
@@ -4529,7 +4563,7 @@
         <v>30.4</v>
       </c>
     </row>
-    <row r="35" spans="1:36" ht="17">
+    <row r="35" ht="17.25" customHeight="1">
       <c r="A35" s="15" t="s">
         <v>59</v>
       </c>
@@ -4552,7 +4586,7 @@
         <v>23</v>
       </c>
       <c r="H35" s="15">
-        <v>40.799999999999997</v>
+        <v>40.8</v>
       </c>
       <c r="I35" s="15">
         <v>74.5</v>
@@ -4576,13 +4610,13 @@
         <v>38.6</v>
       </c>
       <c r="P35" s="15">
-        <v>36.299999999999997</v>
+        <v>36.3</v>
       </c>
       <c r="Q35" s="15">
         <v>16</v>
       </c>
       <c r="R35" s="15">
-        <v>74.099999999999994</v>
+        <v>74.1</v>
       </c>
       <c r="S35" s="15">
         <v>5</v>
@@ -4591,7 +4625,7 @@
         <v>3533</v>
       </c>
       <c r="U35" s="15">
-        <v>74.599999999999994</v>
+        <v>74.6</v>
       </c>
       <c r="V35" s="15">
         <v>9</v>
@@ -4618,7 +4652,7 @@
         <v>27.2</v>
       </c>
       <c r="AD35" s="15">
-        <v>16.899999999999999</v>
+        <v>16.9</v>
       </c>
       <c r="AE35" s="15">
         <v>5</v>
@@ -4639,7 +4673,7 @@
         <v>31.8</v>
       </c>
     </row>
-    <row r="36" spans="1:36" ht="17">
+    <row r="36" ht="17.25" customHeight="1">
       <c r="A36" s="15" t="s">
         <v>60</v>
       </c>
@@ -4674,7 +4708,7 @@
         <v>44.6</v>
       </c>
       <c r="L36" s="15">
-        <v>143.80000000000001</v>
+        <v>143.8</v>
       </c>
       <c r="M36" s="15">
         <v>62.3</v>
@@ -4686,7 +4720,7 @@
         <v>33.1</v>
       </c>
       <c r="P36" s="15">
-        <v>34.700000000000003</v>
+        <v>34.7</v>
       </c>
       <c r="Q36" s="15">
         <v>21</v>
@@ -4731,7 +4765,7 @@
         <v>15.4</v>
       </c>
       <c r="AE36" s="15">
-        <v>4.9000000000000004</v>
+        <v>4.9</v>
       </c>
       <c r="AF36" s="15">
         <v>29</v>
@@ -4749,7 +4783,7 @@
         <v>30.9</v>
       </c>
     </row>
-    <row r="37" spans="1:36" ht="17">
+    <row r="37" ht="17.25" customHeight="1">
       <c r="A37" s="15" t="s">
         <v>61</v>
       </c>
@@ -4829,7 +4863,7 @@
         <v>56</v>
       </c>
       <c r="AA37" s="15">
-        <v>68.099999999999994</v>
+        <v>68.1</v>
       </c>
       <c r="AB37" s="15">
         <v>61.1</v>
@@ -4841,13 +4875,13 @@
         <v>14.6</v>
       </c>
       <c r="AE37" s="15">
-        <v>4.9000000000000004</v>
+        <v>4.9</v>
       </c>
       <c r="AF37" s="15">
         <v>36</v>
       </c>
       <c r="AG37" s="15">
-        <v>78.599999999999994</v>
+        <v>78.6</v>
       </c>
       <c r="AH37" s="15">
         <v>4.54</v>
@@ -4859,7 +4893,7 @@
         <v>29.1</v>
       </c>
     </row>
-    <row r="38" spans="1:36" ht="17">
+    <row r="38" ht="17.25" customHeight="1">
       <c r="A38" s="15" t="s">
         <v>62</v>
       </c>
@@ -4903,10 +4937,10 @@
         <v>17.7</v>
       </c>
       <c r="O38" s="15">
-        <v>35.799999999999997</v>
+        <v>35.8</v>
       </c>
       <c r="P38" s="15">
-        <v>32.700000000000003</v>
+        <v>32.7</v>
       </c>
       <c r="Q38" s="15">
         <v>26</v>
@@ -4969,7 +5003,7 @@
         <v>28.9</v>
       </c>
     </row>
-    <row r="39" spans="1:36" ht="17">
+    <row r="39" ht="17.25" customHeight="1">
       <c r="A39" s="15" t="s">
         <v>63</v>
       </c>
@@ -4986,7 +5020,7 @@
         <v>37</v>
       </c>
       <c r="F39" s="15">
-        <v>71.400000000000006</v>
+        <v>71.4</v>
       </c>
       <c r="G39" s="15">
         <v>24</v>
@@ -4995,7 +5029,7 @@
         <v>42.1</v>
       </c>
       <c r="I39" s="15">
-        <v>75.099999999999994</v>
+        <v>75.1</v>
       </c>
       <c r="J39" s="15">
         <v>22.67</v>
@@ -5013,16 +5047,16 @@
         <v>18.2</v>
       </c>
       <c r="O39" s="15">
-        <v>35.700000000000003</v>
+        <v>35.7</v>
       </c>
       <c r="P39" s="15">
-        <v>32.700000000000003</v>
+        <v>32.7</v>
       </c>
       <c r="Q39" s="15">
         <v>15</v>
       </c>
       <c r="R39" s="15">
-        <v>72.900000000000006</v>
+        <v>72.9</v>
       </c>
       <c r="S39" s="15">
         <v>5</v>
@@ -5031,7 +5065,7 @@
         <v>3498</v>
       </c>
       <c r="U39" s="15">
-        <v>75.599999999999994</v>
+        <v>75.6</v>
       </c>
       <c r="V39" s="15">
         <v>10</v>
@@ -5040,7 +5074,7 @@
         <v>56.1</v>
       </c>
       <c r="X39" s="15">
-        <v>74.900000000000006</v>
+        <v>74.9</v>
       </c>
       <c r="Y39" s="15">
         <v>13.04</v>
@@ -5058,7 +5092,7 @@
         <v>26.7</v>
       </c>
       <c r="AD39" s="15">
-        <v>16.100000000000001</v>
+        <v>16.1</v>
       </c>
       <c r="AE39" s="15">
         <v>4.7</v>
@@ -5079,7 +5113,7 @@
         <v>29.6</v>
       </c>
     </row>
-    <row r="40" spans="1:36" ht="17">
+    <row r="40" ht="17.25" customHeight="1">
       <c r="A40" s="15" t="s">
         <v>64</v>
       </c>
@@ -5105,7 +5139,7 @@
         <v>42.8</v>
       </c>
       <c r="I40" s="15">
-        <v>79.400000000000006</v>
+        <v>79.4</v>
       </c>
       <c r="J40" s="15">
         <v>49.06</v>
@@ -5114,7 +5148,7 @@
         <v>47.3</v>
       </c>
       <c r="L40" s="15">
-        <v>153.69999999999999</v>
+        <v>153.7</v>
       </c>
       <c r="M40" s="15">
         <v>60.3</v>
@@ -5150,7 +5184,7 @@
         <v>55.3</v>
       </c>
       <c r="X40" s="15">
-        <v>79.599999999999994</v>
+        <v>79.6</v>
       </c>
       <c r="Y40" s="15">
         <v>28.479999999999997</v>
@@ -5171,7 +5205,7 @@
         <v>14.2</v>
       </c>
       <c r="AE40" s="15">
-        <v>4.5999999999999996</v>
+        <v>4.6</v>
       </c>
       <c r="AF40" s="15">
         <v>31</v>
@@ -5189,7 +5223,7 @@
         <v>27.8</v>
       </c>
     </row>
-    <row r="41" spans="1:36" ht="17">
+    <row r="41" ht="17.25" customHeight="1">
       <c r="A41" s="15" t="s">
         <v>65</v>
       </c>
@@ -5281,7 +5315,7 @@
         <v>13.9</v>
       </c>
       <c r="AE41" s="15">
-        <v>4.4000000000000004</v>
+        <v>4.4</v>
       </c>
       <c r="AF41" s="15">
         <v>40</v>
@@ -5290,7 +5324,7 @@
         <v>83.8</v>
       </c>
       <c r="AH41" s="15">
-        <v>4.0599999999999996</v>
+        <v>4.06</v>
       </c>
       <c r="AI41" s="15">
         <v>62</v>
@@ -5299,7 +5333,7 @@
         <v>26.4</v>
       </c>
     </row>
-    <row r="42" spans="1:36" ht="17">
+    <row r="42" ht="17.25" customHeight="1">
       <c r="A42" s="15" t="s">
         <v>66</v>
       </c>
@@ -5343,7 +5377,7 @@
         <v>20.8</v>
       </c>
       <c r="O42" s="15">
-        <v>34.200000000000003</v>
+        <v>34.2</v>
       </c>
       <c r="P42" s="15">
         <v>30.1</v>
@@ -5409,7 +5443,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="43" spans="1:36" ht="17">
+    <row r="43" ht="17.25" customHeight="1">
       <c r="A43" s="15" t="s">
         <v>67</v>
       </c>
@@ -5435,7 +5469,7 @@
         <v>41.7</v>
       </c>
       <c r="I43" s="15">
-        <v>75.900000000000006</v>
+        <v>75.9</v>
       </c>
       <c r="J43" s="15">
         <v>22.76</v>
@@ -5453,7 +5487,7 @@
         <v>19.8</v>
       </c>
       <c r="O43" s="15">
-        <v>33.700000000000003</v>
+        <v>33.7</v>
       </c>
       <c r="P43" s="15">
         <v>30.4</v>
@@ -5492,7 +5526,7 @@
         <v>51.8</v>
       </c>
       <c r="AB43" s="15">
-        <v>64.400000000000006</v>
+        <v>64.4</v>
       </c>
       <c r="AC43" s="15">
         <v>26.9</v>
@@ -5501,13 +5535,13 @@
         <v>16.2</v>
       </c>
       <c r="AE43" s="15">
-        <v>4.4000000000000004</v>
+        <v>4.4</v>
       </c>
       <c r="AF43" s="15">
         <v>24</v>
       </c>
       <c r="AG43" s="15">
-        <v>77.400000000000006</v>
+        <v>77.4</v>
       </c>
       <c r="AH43" s="15">
         <v>1.52</v>
@@ -5519,7 +5553,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="44" spans="1:36" ht="17">
+    <row r="44" ht="17.25" customHeight="1">
       <c r="A44" s="15" t="s">
         <v>68</v>
       </c>
@@ -5545,7 +5579,7 @@
         <v>42.8</v>
       </c>
       <c r="I44" s="15">
-        <v>80.900000000000006</v>
+        <v>80.9</v>
       </c>
       <c r="J44" s="15">
         <v>49.66</v>
@@ -5590,7 +5624,7 @@
         <v>57.7</v>
       </c>
       <c r="X44" s="15">
-        <v>80.400000000000006</v>
+        <v>80.4</v>
       </c>
       <c r="Y44" s="15">
         <v>30.04</v>
@@ -5599,7 +5633,7 @@
         <v>55.1</v>
       </c>
       <c r="AA44" s="15">
-        <v>64.099999999999994</v>
+        <v>64.1</v>
       </c>
       <c r="AB44" s="15">
         <v>67.3</v>
@@ -5611,7 +5645,7 @@
         <v>13.8</v>
       </c>
       <c r="AE44" s="15">
-        <v>4.4000000000000004</v>
+        <v>4.4</v>
       </c>
       <c r="AF44" s="15">
         <v>34</v>
@@ -5629,7 +5663,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="45" spans="1:36" ht="17">
+    <row r="45" ht="17.25" customHeight="1">
       <c r="A45" s="15" t="s">
         <v>69</v>
       </c>
@@ -5652,7 +5686,7 @@
         <v>43</v>
       </c>
       <c r="H45" s="15">
-        <v>40.799999999999997</v>
+        <v>40.8</v>
       </c>
       <c r="I45" s="15">
         <v>85.4</v>
@@ -5730,7 +5764,7 @@
         <v>86.1</v>
       </c>
       <c r="AH45" s="15">
-        <v>4.1900000000000004</v>
+        <v>4.19</v>
       </c>
       <c r="AI45" s="15">
         <v>60.6</v>
@@ -5739,7 +5773,7 @@
         <v>25.7</v>
       </c>
     </row>
-    <row r="46" spans="1:36" ht="17">
+    <row r="46" ht="17.25" customHeight="1">
       <c r="A46" s="15" t="s">
         <v>70</v>
       </c>
@@ -5849,7 +5883,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="47" spans="1:36" ht="17">
+    <row r="47" ht="17.25" customHeight="1">
       <c r="A47" s="15" t="s">
         <v>71</v>
       </c>
@@ -5866,7 +5900,7 @@
         <v>45</v>
       </c>
       <c r="F47" s="15">
-        <v>79.599999999999994</v>
+        <v>79.6</v>
       </c>
       <c r="G47" s="15">
         <v>25</v>
@@ -5911,7 +5945,7 @@
         <v>3423</v>
       </c>
       <c r="U47" s="15">
-        <v>76.599999999999994</v>
+        <v>76.6</v>
       </c>
       <c r="V47" s="15">
         <v>10</v>
@@ -5932,7 +5966,7 @@
         <v>53.3</v>
       </c>
       <c r="AB47" s="15">
-        <v>66.400000000000006</v>
+        <v>66.4</v>
       </c>
       <c r="AC47" s="15">
         <v>23.4</v>
@@ -5959,7 +5993,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="48" spans="1:36" ht="17">
+    <row r="48" ht="17.25" customHeight="1">
       <c r="A48" s="15" t="s">
         <v>72</v>
       </c>
@@ -5976,7 +6010,7 @@
         <v>46</v>
       </c>
       <c r="F48" s="15">
-        <v>80.599999999999994</v>
+        <v>80.6</v>
       </c>
       <c r="G48" s="15">
         <v>35</v>
@@ -6069,7 +6103,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="49" spans="1:36" ht="17">
+    <row r="49" ht="17.25" customHeight="1">
       <c r="A49" s="15" t="s">
         <v>73</v>
       </c>
@@ -6152,7 +6186,7 @@
         <v>76</v>
       </c>
       <c r="AB49" s="15">
-        <v>66.599999999999994</v>
+        <v>66.6</v>
       </c>
       <c r="AC49" s="15">
         <v>27.6</v>
@@ -6179,7 +6213,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="50" spans="1:36" ht="17">
+    <row r="50" ht="17.25" customHeight="1">
       <c r="A50" s="15" t="s">
         <v>74</v>
       </c>
@@ -6259,7 +6293,7 @@
         <v>57.5</v>
       </c>
       <c r="AA50" s="15">
-        <v>64.400000000000006</v>
+        <v>64.4</v>
       </c>
       <c r="AB50" s="15">
         <v>66.7</v>
@@ -6289,7 +6323,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="51" spans="1:36" ht="17">
+    <row r="51" ht="17.25" customHeight="1">
       <c r="A51" s="15" t="s">
         <v>75</v>
       </c>
@@ -6342,7 +6376,7 @@
         <v>16</v>
       </c>
       <c r="R51" s="15">
-        <v>77.900000000000006</v>
+        <v>77.9</v>
       </c>
       <c r="S51" s="15">
         <v>5</v>
@@ -6351,7 +6385,7 @@
         <v>3095</v>
       </c>
       <c r="U51" s="15">
-        <v>78.900000000000006</v>
+        <v>78.9</v>
       </c>
       <c r="V51" s="15">
         <v>11</v>
@@ -6372,7 +6406,7 @@
         <v>56.9</v>
       </c>
       <c r="AB51" s="15">
-        <v>65.900000000000006</v>
+        <v>65.9</v>
       </c>
       <c r="AC51" s="15">
         <v>24.3</v>
@@ -6399,7 +6433,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="52" spans="1:36" ht="17">
+    <row r="52" ht="17.25" customHeight="1">
       <c r="A52" s="15" t="s">
         <v>76</v>
       </c>
@@ -6416,7 +6450,7 @@
         <v>50</v>
       </c>
       <c r="F52" s="15">
-        <v>79.900000000000006</v>
+        <v>79.9</v>
       </c>
       <c r="G52" s="15">
         <v>36</v>
@@ -6452,7 +6486,7 @@
         <v>23</v>
       </c>
       <c r="R52" s="15">
-        <v>80.099999999999994</v>
+        <v>80.1</v>
       </c>
       <c r="S52" s="15">
         <v>11</v>
@@ -6482,7 +6516,7 @@
         <v>74.2</v>
       </c>
       <c r="AB52" s="15">
-        <v>66.599999999999994</v>
+        <v>66.6</v>
       </c>
       <c r="AC52" s="15">
         <v>28.6</v>
@@ -6497,7 +6531,7 @@
         <v>33</v>
       </c>
       <c r="AG52" s="15">
-        <v>77.900000000000006</v>
+        <v>77.9</v>
       </c>
       <c r="AH52" s="15">
         <v>3.33</v>
@@ -6509,7 +6543,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="53" spans="1:36" ht="17">
+    <row r="53" ht="17.25" customHeight="1">
       <c r="A53" s="15" t="s">
         <v>77</v>
       </c>
@@ -6613,13 +6647,13 @@
         <v>4.38</v>
       </c>
       <c r="AI53" s="15">
-        <v>64.900000000000006</v>
+        <v>64.9</v>
       </c>
       <c r="AJ53" s="15">
         <v>23.8</v>
       </c>
     </row>
-    <row r="54" spans="1:36" ht="17">
+    <row r="54" ht="17.25" customHeight="1">
       <c r="A54" s="15" t="s">
         <v>78</v>
       </c>
@@ -6723,13 +6757,13 @@
         <v>3.28</v>
       </c>
       <c r="AI54" s="15">
-        <v>66.099999999999994</v>
+        <v>66.1</v>
       </c>
       <c r="AJ54" s="15">
         <v>22.4</v>
       </c>
     </row>
-    <row r="55" spans="1:36" ht="17">
+    <row r="55" ht="17.25" customHeight="1">
       <c r="A55" s="15" t="s">
         <v>79</v>
       </c>
@@ -6746,7 +6780,7 @@
         <v>53</v>
       </c>
       <c r="F55" s="15">
-        <v>78.900000000000006</v>
+        <v>78.9</v>
       </c>
       <c r="G55" s="15">
         <v>26</v>
@@ -6803,7 +6837,7 @@
         <v>79.8</v>
       </c>
       <c r="Y55" s="15">
-        <v>16.170000000000002</v>
+        <v>16.17</v>
       </c>
       <c r="Z55" s="15">
         <v>58.4</v>
@@ -6821,13 +6855,13 @@
         <v>13.4</v>
       </c>
       <c r="AE55" s="15">
-        <v>4.0999999999999996</v>
+        <v>4.1</v>
       </c>
       <c r="AF55" s="15">
         <v>25</v>
       </c>
       <c r="AG55" s="15">
-        <v>76.900000000000006</v>
+        <v>76.9</v>
       </c>
       <c r="AH55" s="15">
         <v>1.62</v>
@@ -6839,7 +6873,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="56" spans="1:36" ht="17">
+    <row r="56" ht="17.25" customHeight="1">
       <c r="A56" s="15" t="s">
         <v>80</v>
       </c>
@@ -6874,7 +6908,7 @@
         <v>47.4</v>
       </c>
       <c r="L56" s="15">
-        <v>158.80000000000001</v>
+        <v>158.8</v>
       </c>
       <c r="M56" s="15">
         <v>61.4</v>
@@ -6901,7 +6935,7 @@
         <v>3732</v>
       </c>
       <c r="U56" s="15">
-        <v>78.599999999999994</v>
+        <v>78.6</v>
       </c>
       <c r="V56" s="15">
         <v>15</v>
@@ -6913,7 +6947,7 @@
         <v>81.7</v>
       </c>
       <c r="Y56" s="15">
-        <v>34.409999999999997</v>
+        <v>34.41</v>
       </c>
       <c r="Z56" s="15">
         <v>59.1</v>
@@ -6937,19 +6971,19 @@
         <v>36</v>
       </c>
       <c r="AG56" s="15">
-        <v>80.900000000000006</v>
+        <v>80.9</v>
       </c>
       <c r="AH56" s="15">
         <v>3.48</v>
       </c>
       <c r="AI56" s="15">
-        <v>66.599999999999994</v>
+        <v>66.6</v>
       </c>
       <c r="AJ56" s="15">
         <v>24.5</v>
       </c>
     </row>
-    <row r="57" spans="1:36" ht="17">
+    <row r="57" ht="17.25" customHeight="1">
       <c r="A57" s="15" t="s">
         <v>81</v>
       </c>
@@ -7050,16 +7084,16 @@
         <v>84.7</v>
       </c>
       <c r="AH57" s="15">
-        <v>4.1100000000000003</v>
+        <v>4.11</v>
       </c>
       <c r="AI57" s="15">
-        <v>66.400000000000006</v>
+        <v>66.4</v>
       </c>
       <c r="AJ57" s="15">
         <v>22.8</v>
       </c>
     </row>
-    <row r="58" spans="1:36" ht="17">
+    <row r="58" ht="17.25" customHeight="1">
       <c r="A58" s="15" t="s">
         <v>82</v>
       </c>
@@ -7142,7 +7176,7 @@
         <v>79.5</v>
       </c>
       <c r="AB58" s="15">
-        <v>70.099999999999994</v>
+        <v>70.1</v>
       </c>
       <c r="AC58" s="15">
         <v>24.1</v>
@@ -7163,13 +7197,13 @@
         <v>3.29</v>
       </c>
       <c r="AI58" s="15">
-        <v>66.099999999999994</v>
+        <v>66.1</v>
       </c>
       <c r="AJ58" s="15">
         <v>22.1</v>
       </c>
     </row>
-    <row r="59" spans="1:36" ht="17">
+    <row r="59" ht="17.25" customHeight="1">
       <c r="A59" s="15" t="s">
         <v>83</v>
       </c>
@@ -7186,7 +7220,7 @@
         <v>57</v>
       </c>
       <c r="F59" s="15">
-        <v>76.400000000000006</v>
+        <v>76.4</v>
       </c>
       <c r="G59" s="15">
         <v>28</v>
@@ -7204,7 +7238,7 @@
         <v>48</v>
       </c>
       <c r="L59" s="15">
-        <v>128.19999999999999</v>
+        <v>128.2</v>
       </c>
       <c r="M59" s="15">
         <v>62.7</v>
@@ -7222,7 +7256,7 @@
         <v>17</v>
       </c>
       <c r="R59" s="15">
-        <v>75.400000000000006</v>
+        <v>75.4</v>
       </c>
       <c r="S59" s="15">
         <v>6</v>
@@ -7231,7 +7265,7 @@
         <v>3166</v>
       </c>
       <c r="U59" s="15">
-        <v>77.099999999999994</v>
+        <v>77.1</v>
       </c>
       <c r="V59" s="15">
         <v>11</v>
@@ -7252,7 +7286,7 @@
         <v>64.3</v>
       </c>
       <c r="AB59" s="15">
-        <v>68.599999999999994</v>
+        <v>68.6</v>
       </c>
       <c r="AC59" s="15">
         <v>23.5</v>
@@ -7267,19 +7301,19 @@
         <v>25</v>
       </c>
       <c r="AG59" s="15">
-        <v>78.599999999999994</v>
+        <v>78.6</v>
       </c>
       <c r="AH59" s="15">
         <v>1.61</v>
       </c>
       <c r="AI59" s="15">
-        <v>65.099999999999994</v>
+        <v>65.1</v>
       </c>
       <c r="AJ59" s="15">
         <v>23.1</v>
       </c>
     </row>
-    <row r="60" spans="1:36" ht="17">
+    <row r="60" ht="17.25" customHeight="1">
       <c r="A60" s="15" t="s">
         <v>84</v>
       </c>
@@ -7296,7 +7330,7 @@
         <v>58</v>
       </c>
       <c r="F60" s="15">
-        <v>80.599999999999994</v>
+        <v>80.6</v>
       </c>
       <c r="G60" s="15">
         <v>37</v>
@@ -7314,7 +7348,7 @@
         <v>45.3</v>
       </c>
       <c r="L60" s="15">
-        <v>143.80000000000001</v>
+        <v>143.8</v>
       </c>
       <c r="M60" s="15">
         <v>59.1</v>
@@ -7332,7 +7366,7 @@
         <v>23</v>
       </c>
       <c r="R60" s="15">
-        <v>80.599999999999994</v>
+        <v>80.6</v>
       </c>
       <c r="S60" s="15">
         <v>7</v>
@@ -7362,7 +7396,7 @@
         <v>62.8</v>
       </c>
       <c r="AB60" s="15">
-        <v>67.099999999999994</v>
+        <v>67.1</v>
       </c>
       <c r="AC60" s="15">
         <v>26.6</v>
@@ -7371,7 +7405,7 @@
         <v>10.6</v>
       </c>
       <c r="AE60" s="15">
-        <v>4.0999999999999996</v>
+        <v>4.1</v>
       </c>
       <c r="AF60" s="15">
         <v>29</v>
@@ -7389,7 +7423,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="61" spans="1:36" ht="17">
+    <row r="61" ht="17.25" customHeight="1">
       <c r="A61" s="15" t="s">
         <v>85</v>
       </c>
@@ -7418,7 +7452,7 @@
         <v>86.3</v>
       </c>
       <c r="J61" s="15">
-        <v>69.039999999999992</v>
+        <v>69.03999999999999</v>
       </c>
       <c r="K61" s="15">
         <v>45.7</v>
@@ -7469,10 +7503,10 @@
         <v>61.1</v>
       </c>
       <c r="AA61" s="15">
-        <v>79.400000000000006</v>
+        <v>79.4</v>
       </c>
       <c r="AB61" s="15">
-        <v>67.099999999999994</v>
+        <v>67.1</v>
       </c>
       <c r="AC61" s="15">
         <v>27.4</v>
@@ -7493,13 +7527,13 @@
         <v>3.85</v>
       </c>
       <c r="AI61" s="15">
-        <v>65.099999999999994</v>
+        <v>65.1</v>
       </c>
       <c r="AJ61" s="15">
         <v>23.2</v>
       </c>
     </row>
-    <row r="62" spans="1:36" ht="17">
+    <row r="62" ht="17.25" customHeight="1">
       <c r="A62" s="15" t="s">
         <v>86</v>
       </c>
@@ -7603,13 +7637,13 @@
         <v>3.35</v>
       </c>
       <c r="AI62" s="15">
-        <v>65.599999999999994</v>
+        <v>65.6</v>
       </c>
       <c r="AJ62" s="15">
         <v>22.1</v>
       </c>
     </row>
-    <row r="63" spans="1:36" ht="17">
+    <row r="63" ht="17.25" customHeight="1">
       <c r="A63" s="15" t="s">
         <v>87</v>
       </c>
@@ -7626,7 +7660,7 @@
         <v>61</v>
       </c>
       <c r="F63" s="15">
-        <v>74.599999999999994</v>
+        <v>74.6</v>
       </c>
       <c r="G63" s="15">
         <v>28</v>
@@ -7680,7 +7714,7 @@
         <v>60.5</v>
       </c>
       <c r="X63" s="15">
-        <v>76.599999999999994</v>
+        <v>76.6</v>
       </c>
       <c r="Y63" s="15">
         <v>16.84</v>
@@ -7692,7 +7726,7 @@
         <v>72.8</v>
       </c>
       <c r="AB63" s="15">
-        <v>70.900000000000006</v>
+        <v>70.9</v>
       </c>
       <c r="AC63" s="15">
         <v>26.7</v>
@@ -7707,7 +7741,7 @@
         <v>24</v>
       </c>
       <c r="AG63" s="15">
-        <v>78.900000000000006</v>
+        <v>78.9</v>
       </c>
       <c r="AH63" s="15">
         <v>1.61</v>
@@ -7719,7 +7753,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="64" spans="1:36" ht="17">
+    <row r="64" ht="17.25" customHeight="1">
       <c r="A64" s="15" t="s">
         <v>88</v>
       </c>
@@ -7790,10 +7824,10 @@
         <v>60.9</v>
       </c>
       <c r="X64" s="15">
-        <v>81.400000000000006</v>
+        <v>81.4</v>
       </c>
       <c r="Y64" s="15">
-        <v>37.159999999999997</v>
+        <v>37.16</v>
       </c>
       <c r="Z64" s="15">
         <v>61.9</v>
@@ -7811,7 +7845,7 @@
         <v>10.5</v>
       </c>
       <c r="AE64" s="15">
-        <v>4.0999999999999996</v>
+        <v>4.1</v>
       </c>
       <c r="AF64" s="15">
         <v>35</v>
@@ -7823,13 +7857,13 @@
         <v>3.63</v>
       </c>
       <c r="AI64" s="15">
-        <v>66.099999999999994</v>
+        <v>66.1</v>
       </c>
       <c r="AJ64" s="15">
         <v>22.1</v>
       </c>
     </row>
-    <row r="65" spans="1:36" ht="17">
+    <row r="65" ht="17.25" customHeight="1">
       <c r="A65" s="15" t="s">
         <v>89</v>
       </c>
@@ -7930,7 +7964,7 @@
         <v>86</v>
       </c>
       <c r="AH65" s="15">
-        <v>4.3099999999999996</v>
+        <v>4.31</v>
       </c>
       <c r="AI65" s="15">
         <v>63.8</v>
@@ -7939,7 +7973,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="66" spans="1:36" ht="17">
+    <row r="66" ht="17.25" customHeight="1">
       <c r="A66" s="15" t="s">
         <v>90</v>
       </c>
@@ -8013,7 +8047,7 @@
         <v>91.6</v>
       </c>
       <c r="Y66" s="15">
-        <v>34.659999999999997</v>
+        <v>34.66</v>
       </c>
       <c r="Z66" s="15">
         <v>63.8</v>
@@ -8049,7 +8083,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="67" spans="1:36" ht="17">
+    <row r="67" ht="17.25" customHeight="1">
       <c r="A67" s="15" t="s">
         <v>91</v>
       </c>
@@ -8087,13 +8121,13 @@
         <v>136.6</v>
       </c>
       <c r="M67" s="15">
-        <v>65.099999999999994</v>
+        <v>65.1</v>
       </c>
       <c r="N67" s="15">
-        <v>20.100000000000001</v>
+        <v>20.1</v>
       </c>
       <c r="O67" s="15">
-        <v>34.200000000000003</v>
+        <v>34.2</v>
       </c>
       <c r="P67" s="15">
         <v>29.3</v>
@@ -8111,7 +8145,7 @@
         <v>3112</v>
       </c>
       <c r="U67" s="15">
-        <v>76.099999999999994</v>
+        <v>76.1</v>
       </c>
       <c r="V67" s="15">
         <v>10</v>
@@ -8129,7 +8163,7 @@
         <v>59.9</v>
       </c>
       <c r="AA67" s="15">
-        <v>67.599999999999994</v>
+        <v>67.6</v>
       </c>
       <c r="AB67" s="15">
         <v>69.7</v>
@@ -8159,7 +8193,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="68" spans="1:36" ht="17">
+    <row r="68" ht="17.25" customHeight="1">
       <c r="A68" s="15" t="s">
         <v>92</v>
       </c>
@@ -8251,7 +8285,7 @@
         <v>10.5</v>
       </c>
       <c r="AE68" s="15">
-        <v>4.0999999999999996</v>
+        <v>4.1</v>
       </c>
       <c r="AF68" s="15">
         <v>38</v>
@@ -8269,7 +8303,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="69" spans="1:36" ht="17">
+    <row r="69" ht="17.25" customHeight="1">
       <c r="A69" s="15" t="s">
         <v>93</v>
       </c>
@@ -8310,7 +8344,7 @@
         <v>63.6</v>
       </c>
       <c r="N69" s="15">
-        <v>19.399999999999999</v>
+        <v>19.4</v>
       </c>
       <c r="O69" s="15">
         <v>27.1</v>
@@ -8358,7 +8392,7 @@
         <v>28.1</v>
       </c>
       <c r="AD69" s="15">
-        <v>9.1999999999999993</v>
+        <v>9.2</v>
       </c>
       <c r="AE69" s="15">
         <v>4</v>
@@ -8379,7 +8413,7 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="70" spans="1:36" ht="17">
+    <row r="70" ht="17.25" customHeight="1">
       <c r="A70" s="15" t="s">
         <v>94</v>
       </c>
@@ -8489,7 +8523,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="71" spans="1:36" ht="17">
+    <row r="71" ht="17.25" customHeight="1">
       <c r="A71" s="15" t="s">
         <v>95</v>
       </c>
@@ -8515,7 +8549,7 @@
         <v>51.6</v>
       </c>
       <c r="I71" s="15">
-        <v>77.599999999999994</v>
+        <v>77.6</v>
       </c>
       <c r="J71" s="15">
         <v>26.84</v>
@@ -8527,7 +8561,7 @@
         <v>151.6</v>
       </c>
       <c r="M71" s="15">
-        <v>66.900000000000006</v>
+        <v>66.9</v>
       </c>
       <c r="N71" s="15">
         <v>22.3</v>
@@ -8542,7 +8576,7 @@
         <v>20</v>
       </c>
       <c r="R71" s="15">
-        <v>77.900000000000006</v>
+        <v>77.9</v>
       </c>
       <c r="S71" s="15">
         <v>6</v>
@@ -8551,7 +8585,7 @@
         <v>3308</v>
       </c>
       <c r="U71" s="15">
-        <v>76.400000000000006</v>
+        <v>76.4</v>
       </c>
       <c r="V71" s="15">
         <v>11</v>
@@ -8560,7 +8594,7 @@
         <v>59.2</v>
       </c>
       <c r="X71" s="15">
-        <v>79.400000000000006</v>
+        <v>79.4</v>
       </c>
       <c r="Y71" s="15">
         <v>16.810000000000002</v>
@@ -8587,7 +8621,7 @@
         <v>26</v>
       </c>
       <c r="AG71" s="15">
-        <v>75.900000000000006</v>
+        <v>75.9</v>
       </c>
       <c r="AH71" s="15">
         <v>1.62</v>
@@ -8599,7 +8633,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="72" spans="1:36" ht="17">
+    <row r="72" ht="17.25" customHeight="1">
       <c r="A72" s="15" t="s">
         <v>96</v>
       </c>
@@ -8628,7 +8662,7 @@
         <v>81.8</v>
       </c>
       <c r="J72" s="15">
-        <v>60.789999999999992</v>
+        <v>60.78999999999999</v>
       </c>
       <c r="K72" s="15">
         <v>48.2</v>
@@ -8637,7 +8671,7 @@
         <v>187.9</v>
       </c>
       <c r="M72" s="15">
-        <v>67.400000000000006</v>
+        <v>67.4</v>
       </c>
       <c r="N72" s="15">
         <v>21.7</v>
@@ -8673,7 +8707,7 @@
         <v>85.1</v>
       </c>
       <c r="Y72" s="15">
-        <v>37.200000000000003</v>
+        <v>37.2</v>
       </c>
       <c r="Z72" s="15">
         <v>62.5</v>
@@ -8682,7 +8716,7 @@
         <v>88.5</v>
       </c>
       <c r="AB72" s="15">
-        <v>69.599999999999994</v>
+        <v>69.6</v>
       </c>
       <c r="AC72" s="15">
         <v>27.2</v>
@@ -8709,7 +8743,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="73" spans="1:36" ht="17">
+    <row r="73" ht="17.25" customHeight="1">
       <c r="A73" s="15" t="s">
         <v>97</v>
       </c>
@@ -8813,13 +8847,13 @@
         <v>4.88</v>
       </c>
       <c r="AI73" s="15">
-        <v>66.099999999999994</v>
+        <v>66.1</v>
       </c>
       <c r="AJ73" s="15">
         <v>22.1</v>
       </c>
     </row>
-    <row r="74" spans="1:36" ht="17">
+    <row r="74" ht="17.25" customHeight="1">
       <c r="A74" s="15" t="s">
         <v>98</v>
       </c>
@@ -8857,7 +8891,7 @@
         <v>189.9</v>
       </c>
       <c r="M74" s="15">
-        <v>66.599999999999994</v>
+        <v>66.6</v>
       </c>
       <c r="N74" s="15">
         <v>17.8</v>
@@ -8902,7 +8936,7 @@
         <v>74.7</v>
       </c>
       <c r="AB74" s="15">
-        <v>71.099999999999994</v>
+        <v>71.1</v>
       </c>
       <c r="AC74" s="15">
         <v>28.6</v>
@@ -8929,7 +8963,7 @@
         <v>19.2</v>
       </c>
     </row>
-    <row r="75" spans="1:36" ht="17">
+    <row r="75" ht="17.25" customHeight="1">
       <c r="A75" s="15" t="s">
         <v>99</v>
       </c>
@@ -8946,7 +8980,7 @@
         <v>73</v>
       </c>
       <c r="F75" s="15">
-        <v>79.099999999999994</v>
+        <v>79.1</v>
       </c>
       <c r="G75" s="15">
         <v>36</v>
@@ -8955,7 +8989,7 @@
         <v>48.5</v>
       </c>
       <c r="I75" s="15">
-        <v>73.900000000000006</v>
+        <v>73.9</v>
       </c>
       <c r="J75" s="15">
         <v>26.990000000000002</v>
@@ -8967,7 +9001,7 @@
         <v>174.9</v>
       </c>
       <c r="M75" s="15">
-        <v>68.900000000000006</v>
+        <v>68.9</v>
       </c>
       <c r="N75" s="15">
         <v>21.8</v>
@@ -8982,7 +9016,7 @@
         <v>19</v>
       </c>
       <c r="R75" s="15">
-        <v>75.599999999999994</v>
+        <v>75.6</v>
       </c>
       <c r="S75" s="15">
         <v>5</v>
@@ -9000,7 +9034,7 @@
         <v>60.4</v>
       </c>
       <c r="X75" s="15">
-        <v>79.099999999999994</v>
+        <v>79.1</v>
       </c>
       <c r="Y75" s="15">
         <v>17.09</v>
@@ -9027,7 +9061,7 @@
         <v>29</v>
       </c>
       <c r="AG75" s="15">
-        <v>77.400000000000006</v>
+        <v>77.4</v>
       </c>
       <c r="AH75" s="15">
         <v>1.87</v>
@@ -9039,7 +9073,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="76" spans="1:36" ht="17">
+    <row r="76" ht="17.25" customHeight="1">
       <c r="A76" s="15" t="s">
         <v>100</v>
       </c>
@@ -9077,7 +9111,7 @@
         <v>202.2</v>
       </c>
       <c r="M76" s="15">
-        <v>66.400000000000006</v>
+        <v>66.4</v>
       </c>
       <c r="N76" s="15">
         <v>18.7</v>
@@ -9113,7 +9147,7 @@
         <v>82.7</v>
       </c>
       <c r="Y76" s="15">
-        <v>38.340000000000003</v>
+        <v>38.34</v>
       </c>
       <c r="Z76" s="15">
         <v>62.5</v>
@@ -9128,7 +9162,7 @@
         <v>30.1</v>
       </c>
       <c r="AD76" s="15">
-        <v>9.3000000000000007</v>
+        <v>9.3</v>
       </c>
       <c r="AE76" s="15">
         <v>3.4</v>
@@ -9149,7 +9183,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="77" spans="1:36" ht="17">
+    <row r="77" ht="17.25" customHeight="1">
       <c r="A77" s="15" t="s">
         <v>101</v>
       </c>
@@ -9178,7 +9212,7 @@
         <v>85.1</v>
       </c>
       <c r="J77" s="15">
-        <v>69.569999999999993</v>
+        <v>69.57</v>
       </c>
       <c r="K77" s="15">
         <v>50.4</v>
@@ -9190,7 +9224,7 @@
         <v>67.3</v>
       </c>
       <c r="N77" s="15">
-        <v>18.100000000000001</v>
+        <v>18.1</v>
       </c>
       <c r="O77" s="15">
         <v>24.4</v>
@@ -9238,7 +9272,7 @@
         <v>31</v>
       </c>
       <c r="AD77" s="15">
-        <v>9.8000000000000007</v>
+        <v>9.8</v>
       </c>
       <c r="AE77" s="15">
         <v>3.2</v>
@@ -9250,7 +9284,7 @@
         <v>88.2</v>
       </c>
       <c r="AH77" s="15">
-        <v>5.0999999999999996</v>
+        <v>5.1</v>
       </c>
       <c r="AI77" s="15">
         <v>64.8</v>
@@ -9259,7 +9293,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="78" spans="1:36" ht="17">
+    <row r="78" ht="17.25" customHeight="1">
       <c r="A78" s="15" t="s">
         <v>102</v>
       </c>
@@ -9342,7 +9376,7 @@
         <v>83.5</v>
       </c>
       <c r="AB78" s="15">
-        <v>69.400000000000006</v>
+        <v>69.4</v>
       </c>
       <c r="AC78" s="15">
         <v>29.4</v>
@@ -9366,10 +9400,10 @@
         <v>63.4</v>
       </c>
       <c r="AJ78" s="15">
-        <v>18.600000000000001</v>
+        <v>18.6</v>
       </c>
     </row>
-    <row r="79" spans="1:36" ht="17">
+    <row r="79" ht="17.25" customHeight="1">
       <c r="A79" s="15" t="s">
         <v>103</v>
       </c>
@@ -9386,7 +9420,7 @@
         <v>77</v>
       </c>
       <c r="F79" s="15">
-        <v>79.900000000000006</v>
+        <v>79.9</v>
       </c>
       <c r="G79" s="15">
         <v>36</v>
@@ -9395,7 +9429,7 @@
         <v>49.7</v>
       </c>
       <c r="I79" s="15">
-        <v>79.099999999999994</v>
+        <v>79.1</v>
       </c>
       <c r="J79" s="15">
         <v>26.450000000000003</v>
@@ -9410,7 +9444,7 @@
         <v>70</v>
       </c>
       <c r="N79" s="15">
-        <v>18.399999999999999</v>
+        <v>18.4</v>
       </c>
       <c r="O79" s="15">
         <v>30.4</v>
@@ -9440,7 +9474,7 @@
         <v>60.5</v>
       </c>
       <c r="X79" s="15">
-        <v>75.400000000000006</v>
+        <v>75.4</v>
       </c>
       <c r="Y79" s="15">
         <v>17.509999999999998</v>
@@ -9449,7 +9483,7 @@
         <v>64.3</v>
       </c>
       <c r="AA79" s="15">
-        <v>73.900000000000006</v>
+        <v>73.9</v>
       </c>
       <c r="AB79" s="15">
         <v>71</v>
@@ -9476,10 +9510,10 @@
         <v>64.5</v>
       </c>
       <c r="AJ79" s="15">
-        <v>18.600000000000001</v>
+        <v>18.6</v>
       </c>
     </row>
-    <row r="80" spans="1:36" ht="17">
+    <row r="80" ht="17.25" customHeight="1">
       <c r="A80" s="15" t="s">
         <v>104</v>
       </c>
@@ -9517,7 +9551,7 @@
         <v>227.6</v>
       </c>
       <c r="M80" s="15">
-        <v>68.400000000000006</v>
+        <v>68.4</v>
       </c>
       <c r="N80" s="15">
         <v>18</v>
@@ -9553,7 +9587,7 @@
         <v>85.5</v>
       </c>
       <c r="Y80" s="15">
-        <v>38.119999999999997</v>
+        <v>38.12</v>
       </c>
       <c r="Z80" s="15">
         <v>63.2</v>
@@ -9586,10 +9620,10 @@
         <v>64.5</v>
       </c>
       <c r="AJ80" s="15">
-        <v>19.100000000000001</v>
+        <v>19.1</v>
       </c>
     </row>
-    <row r="81" spans="1:36" ht="17">
+    <row r="81" ht="17.25" customHeight="1">
       <c r="A81" s="15" t="s">
         <v>105</v>
       </c>
@@ -9627,7 +9661,7 @@
         <v>240.1</v>
       </c>
       <c r="M81" s="15">
-        <v>70.599999999999994</v>
+        <v>70.6</v>
       </c>
       <c r="N81" s="15">
         <v>21.8</v>
@@ -9699,7 +9733,7 @@
         <v>17.8</v>
       </c>
     </row>
-    <row r="82" spans="1:36" ht="17">
+    <row r="82" ht="17.25" customHeight="1">
       <c r="A82" s="15" t="s">
         <v>106</v>
       </c>
@@ -9740,7 +9774,7 @@
         <v>69</v>
       </c>
       <c r="N82" s="15">
-        <v>20.100000000000001</v>
+        <v>20.1</v>
       </c>
       <c r="O82" s="15">
         <v>24.6</v>
@@ -9782,7 +9816,7 @@
         <v>91</v>
       </c>
       <c r="AB82" s="15">
-        <v>70.099999999999994</v>
+        <v>70.1</v>
       </c>
       <c r="AC82" s="15">
         <v>27</v>
@@ -9810,7 +9844,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:Q1"/>
     <mergeCell ref="R1:T1"/>
@@ -9818,6 +9852,13 @@
     <mergeCell ref="X1:AF1"/>
     <mergeCell ref="AG1:AJ1"/>
   </mergeCells>
+  <printOptions/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
+    <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
+  </headerFooter>
+  <extLst/>
 </worksheet>
 </file>